--- a/server/assets/INPUT_DATA_styled.xlsx
+++ b/server/assets/INPUT_DATA_styled.xlsx
@@ -521,7 +521,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -880,9 +880,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="10" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1857,7 +1854,7 @@
     <row r="27" ht="20" customHeight="1" s="59"/>
     <row r="28" ht="22" customHeight="1" s="59">
       <c r="B28" s="98">
-        <f>"산출 기준: 현장 입력값 — 소비전력 "&amp;'절감 산출'!B3&amp;"W · 일일 점등 "&amp;'절감 산출'!B4&amp;"시간 · LED "&amp;TEXT('절감 산출'!B5,"#,##0")&amp;"등 · 전기요금 "&amp;'절감 산출'!B8&amp;"원/kWh · 현재 등 효율 "&amp;'절감 산출'!B13&amp;"lm/W. 고정값 — M-Carbon 등 효율 "&amp;'절감 산출'!B14&amp;"lm/W · Smart IoT 추가 절감 "&amp;TEXT('절감 산출'!B15,"0%")&amp;" · 전기요금 연 5% 상승 · 성과공유 비율(산출 시트 H열). 상세 계산은 ‘절감 산출’ 시트 참고."</f>
+        <f>"산출 기준: 현장 입력값 — 소비전력 "&amp;'절감 산출'!B3&amp;"W · 일일 점등 "&amp;'절감 산출'!B4&amp;"시간 · LED "&amp;TEXT('절감 산출'!B5,"#,##0")&amp;"등 · 전기요금 "&amp;'절감 산출'!B8&amp;"원/kWh · 현재 등 효율 "&amp;'절감 산출'!B13&amp;"lm/W · M-Carbon 등 효율 "&amp;'절감 산출'!B14&amp;"lm/W. 고정값 — Smart IoT 추가 절감 "&amp;TEXT('절감 산출'!B15,"0%")&amp;" · 전기요금 연 5% 상승 · 성과공유 비율(산출 시트 H열). 상세 계산은 ‘절감 산출’ 시트 참고."</f>
         <v/>
       </c>
     </row>
@@ -2463,20 +2460,20 @@
           <t>M-Carbon 등 효율 [lm/W]</t>
         </is>
       </c>
-      <c r="B14" s="126" t="n">
+      <c r="B14" s="125" t="n">
         <v>180</v>
       </c>
       <c r="C14" s="102" t="n"/>
       <c r="D14" s="102" t="n"/>
-      <c r="E14" s="127" t="inlineStr">
+      <c r="E14" s="126" t="inlineStr">
         <is>
           <t>건물주 추가투지비용 절감액</t>
         </is>
       </c>
-      <c r="F14" s="128" t="n"/>
-      <c r="G14" s="128" t="n"/>
-      <c r="H14" s="128" t="n"/>
-      <c r="I14" s="129" t="n"/>
+      <c r="F14" s="127" t="n"/>
+      <c r="G14" s="127" t="n"/>
+      <c r="H14" s="127" t="n"/>
+      <c r="I14" s="128" t="n"/>
       <c r="J14" s="114">
         <f>B42</f>
         <v/>
@@ -2496,24 +2493,24 @@
           <t>Smart IoT추가 절감효율 [%]</t>
         </is>
       </c>
-      <c r="B15" s="130" t="n">
+      <c r="B15" s="129" t="n">
         <v>0.25</v>
       </c>
       <c r="C15" s="102" t="n"/>
       <c r="D15" s="102" t="n"/>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="130" t="inlineStr">
         <is>
           <t>총계</t>
         </is>
       </c>
-      <c r="F15" s="132" t="n"/>
-      <c r="G15" s="132" t="n"/>
-      <c r="H15" s="132" t="n"/>
-      <c r="I15" s="133">
+      <c r="F15" s="131" t="n"/>
+      <c r="G15" s="131" t="n"/>
+      <c r="H15" s="131" t="n"/>
+      <c r="I15" s="132">
         <f>SUM(I4:I13)</f>
         <v/>
       </c>
-      <c r="J15" s="134">
+      <c r="J15" s="133">
         <f>SUM(J4:J14)</f>
         <v/>
       </c>
@@ -2535,8 +2532,8 @@
       <c r="F16" s="102" t="n"/>
       <c r="G16" s="102" t="n"/>
       <c r="H16" s="102" t="n"/>
-      <c r="I16" s="135" t="n"/>
-      <c r="J16" s="135" t="n"/>
+      <c r="I16" s="134" t="n"/>
+      <c r="J16" s="134" t="n"/>
       <c r="K16" s="102" t="n"/>
       <c r="L16" s="102" t="n"/>
       <c r="M16" s="102" t="n"/>
@@ -2552,18 +2549,18 @@
           <t>에너지 Saving Ratio</t>
         </is>
       </c>
-      <c r="B17" s="136">
+      <c r="B17" s="135">
         <f>(B14/B13)-1+B15</f>
         <v/>
       </c>
       <c r="C17" s="102" t="n"/>
       <c r="D17" s="102" t="n"/>
       <c r="E17" s="102" t="n"/>
-      <c r="F17" s="135" t="n"/>
-      <c r="G17" s="137" t="n"/>
-      <c r="H17" s="137" t="n"/>
-      <c r="I17" s="135" t="n"/>
-      <c r="J17" s="135" t="n"/>
+      <c r="F17" s="134" t="n"/>
+      <c r="G17" s="136" t="n"/>
+      <c r="H17" s="136" t="n"/>
+      <c r="I17" s="134" t="n"/>
+      <c r="J17" s="134" t="n"/>
       <c r="K17" s="102" t="n"/>
       <c r="L17" s="102" t="n"/>
       <c r="M17" s="102" t="n"/>
@@ -2579,18 +2576,18 @@
           <t>연간 절감 전력 [kWh]</t>
         </is>
       </c>
-      <c r="B18" s="138">
+      <c r="B18" s="137">
         <f>R4</f>
         <v/>
       </c>
       <c r="C18" s="102" t="n"/>
       <c r="D18" s="102" t="n"/>
       <c r="E18" s="102" t="n"/>
-      <c r="F18" s="135" t="n"/>
-      <c r="G18" s="137" t="n"/>
-      <c r="H18" s="137" t="n"/>
-      <c r="I18" s="135" t="n"/>
-      <c r="J18" s="135" t="n"/>
+      <c r="F18" s="134" t="n"/>
+      <c r="G18" s="136" t="n"/>
+      <c r="H18" s="136" t="n"/>
+      <c r="I18" s="134" t="n"/>
+      <c r="J18" s="134" t="n"/>
       <c r="K18" s="102" t="n"/>
       <c r="L18" s="102" t="n"/>
       <c r="M18" s="102" t="n"/>
@@ -2618,7 +2615,7 @@
       <c r="H19" s="102" t="n"/>
       <c r="I19" s="102" t="n"/>
       <c r="J19" s="102" t="n"/>
-      <c r="K19" s="135" t="n"/>
+      <c r="K19" s="134" t="n"/>
       <c r="L19" s="102" t="n"/>
       <c r="M19" s="102" t="n"/>
       <c r="N19" s="102" t="n"/>
@@ -2629,7 +2626,7 @@
     </row>
     <row r="20" ht="21" customHeight="1" s="59">
       <c r="A20" s="102" t="n"/>
-      <c r="B20" s="135" t="n"/>
+      <c r="B20" s="134" t="n"/>
       <c r="C20" s="102" t="n"/>
       <c r="D20" s="102" t="n"/>
       <c r="E20" s="102" t="n"/>
@@ -2679,7 +2676,7 @@
           <t>회수/10년 기준</t>
         </is>
       </c>
-      <c r="B22" s="139" t="n">
+      <c r="B22" s="138" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="102" t="n"/>
@@ -2732,11 +2729,11 @@
       <c r="C24" s="102" t="n"/>
       <c r="D24" s="102" t="n"/>
       <c r="E24" s="102" t="n"/>
-      <c r="F24" s="135" t="n"/>
-      <c r="G24" s="140" t="n"/>
-      <c r="H24" s="140" t="n"/>
-      <c r="I24" s="135" t="n"/>
-      <c r="J24" s="135" t="n"/>
+      <c r="F24" s="134" t="n"/>
+      <c r="G24" s="139" t="n"/>
+      <c r="H24" s="139" t="n"/>
+      <c r="I24" s="134" t="n"/>
+      <c r="J24" s="134" t="n"/>
       <c r="K24" s="102" t="n"/>
       <c r="L24" s="102" t="n"/>
       <c r="M24" s="102" t="n"/>
@@ -2752,7 +2749,7 @@
           <t>년차별 절감 예상</t>
         </is>
       </c>
-      <c r="B25" s="141" t="inlineStr">
+      <c r="B25" s="140" t="inlineStr">
         <is>
           <t>5% 전기용금 상승 기준</t>
         </is>
@@ -2760,11 +2757,11 @@
       <c r="C25" s="102" t="n"/>
       <c r="D25" s="102" t="n"/>
       <c r="E25" s="102" t="n"/>
-      <c r="F25" s="135" t="n"/>
-      <c r="G25" s="140" t="n"/>
-      <c r="H25" s="140" t="n"/>
-      <c r="I25" s="135" t="n"/>
-      <c r="J25" s="135" t="n"/>
+      <c r="F25" s="134" t="n"/>
+      <c r="G25" s="139" t="n"/>
+      <c r="H25" s="139" t="n"/>
+      <c r="I25" s="134" t="n"/>
+      <c r="J25" s="134" t="n"/>
       <c r="K25" s="102" t="n"/>
       <c r="L25" s="102" t="n"/>
       <c r="M25" s="102" t="n"/>
@@ -2780,11 +2777,11 @@
       <c r="C26" s="102" t="n"/>
       <c r="D26" s="102" t="n"/>
       <c r="E26" s="102" t="n"/>
-      <c r="F26" s="135" t="n"/>
-      <c r="G26" s="140" t="n"/>
-      <c r="H26" s="140" t="n"/>
-      <c r="I26" s="135" t="n"/>
-      <c r="J26" s="135" t="n"/>
+      <c r="F26" s="134" t="n"/>
+      <c r="G26" s="139" t="n"/>
+      <c r="H26" s="139" t="n"/>
+      <c r="I26" s="134" t="n"/>
+      <c r="J26" s="134" t="n"/>
       <c r="K26" s="102" t="n"/>
       <c r="L26" s="102" t="n"/>
       <c r="M26" s="102" t="n"/>
@@ -2798,18 +2795,18 @@
       <c r="A27" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="142">
+      <c r="B27" s="141">
         <f>B19</f>
         <v/>
       </c>
       <c r="C27" s="102" t="n"/>
       <c r="D27" s="102" t="n"/>
       <c r="E27" s="102" t="n"/>
-      <c r="F27" s="135" t="n"/>
-      <c r="G27" s="140" t="n"/>
-      <c r="H27" s="140" t="n"/>
-      <c r="I27" s="135" t="n"/>
-      <c r="J27" s="135" t="n"/>
+      <c r="F27" s="134" t="n"/>
+      <c r="G27" s="139" t="n"/>
+      <c r="H27" s="139" t="n"/>
+      <c r="I27" s="134" t="n"/>
+      <c r="J27" s="134" t="n"/>
       <c r="K27" s="102" t="n"/>
       <c r="L27" s="102" t="n"/>
       <c r="M27" s="102" t="n"/>
@@ -2823,18 +2820,18 @@
       <c r="A28" s="75" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="143">
+      <c r="B28" s="142">
         <f>B27*1.05</f>
         <v/>
       </c>
       <c r="C28" s="102" t="n"/>
       <c r="D28" s="102" t="n"/>
       <c r="E28" s="102" t="n"/>
-      <c r="F28" s="135" t="n"/>
-      <c r="G28" s="140" t="n"/>
-      <c r="H28" s="140" t="n"/>
-      <c r="I28" s="135" t="n"/>
-      <c r="J28" s="135" t="n"/>
+      <c r="F28" s="134" t="n"/>
+      <c r="G28" s="139" t="n"/>
+      <c r="H28" s="139" t="n"/>
+      <c r="I28" s="134" t="n"/>
+      <c r="J28" s="134" t="n"/>
       <c r="K28" s="102" t="n"/>
       <c r="L28" s="102" t="n"/>
       <c r="M28" s="102" t="n"/>
@@ -2848,18 +2845,18 @@
       <c r="A29" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="142">
+      <c r="B29" s="141">
         <f>B28*1.05</f>
         <v/>
       </c>
       <c r="C29" s="102" t="n"/>
       <c r="D29" s="102" t="n"/>
       <c r="E29" s="102" t="n"/>
-      <c r="F29" s="135" t="n"/>
-      <c r="G29" s="140" t="n"/>
-      <c r="H29" s="140" t="n"/>
-      <c r="I29" s="135" t="n"/>
-      <c r="J29" s="135" t="n"/>
+      <c r="F29" s="134" t="n"/>
+      <c r="G29" s="139" t="n"/>
+      <c r="H29" s="139" t="n"/>
+      <c r="I29" s="134" t="n"/>
+      <c r="J29" s="134" t="n"/>
       <c r="K29" s="102" t="n"/>
       <c r="L29" s="102" t="n"/>
       <c r="M29" s="102" t="n"/>
@@ -2873,18 +2870,18 @@
       <c r="A30" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="143">
+      <c r="B30" s="142">
         <f>B29*1.05</f>
         <v/>
       </c>
       <c r="C30" s="102" t="n"/>
       <c r="D30" s="102" t="n"/>
       <c r="E30" s="102" t="n"/>
-      <c r="F30" s="135" t="n"/>
-      <c r="G30" s="140" t="n"/>
-      <c r="H30" s="140" t="n"/>
-      <c r="I30" s="135" t="n"/>
-      <c r="J30" s="135" t="n"/>
+      <c r="F30" s="134" t="n"/>
+      <c r="G30" s="139" t="n"/>
+      <c r="H30" s="139" t="n"/>
+      <c r="I30" s="134" t="n"/>
+      <c r="J30" s="134" t="n"/>
       <c r="K30" s="102" t="n"/>
       <c r="L30" s="102" t="n"/>
       <c r="M30" s="102" t="n"/>
@@ -2898,18 +2895,18 @@
       <c r="A31" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="142">
+      <c r="B31" s="141">
         <f>B30*1.05</f>
         <v/>
       </c>
       <c r="C31" s="102" t="n"/>
       <c r="D31" s="102" t="n"/>
       <c r="E31" s="102" t="n"/>
-      <c r="F31" s="135" t="n"/>
-      <c r="G31" s="140" t="n"/>
-      <c r="H31" s="140" t="n"/>
-      <c r="I31" s="135" t="n"/>
-      <c r="J31" s="135" t="n"/>
+      <c r="F31" s="134" t="n"/>
+      <c r="G31" s="139" t="n"/>
+      <c r="H31" s="139" t="n"/>
+      <c r="I31" s="134" t="n"/>
+      <c r="J31" s="134" t="n"/>
       <c r="K31" s="102" t="n"/>
       <c r="L31" s="102" t="n"/>
       <c r="M31" s="102" t="n"/>
@@ -2923,18 +2920,18 @@
       <c r="A32" s="75" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="143">
+      <c r="B32" s="142">
         <f>B31*1.05</f>
         <v/>
       </c>
       <c r="C32" s="102" t="n"/>
       <c r="D32" s="102" t="n"/>
       <c r="E32" s="102" t="n"/>
-      <c r="F32" s="135" t="n"/>
-      <c r="G32" s="140" t="n"/>
-      <c r="H32" s="140" t="n"/>
-      <c r="I32" s="135" t="n"/>
-      <c r="J32" s="135" t="n"/>
+      <c r="F32" s="134" t="n"/>
+      <c r="G32" s="139" t="n"/>
+      <c r="H32" s="139" t="n"/>
+      <c r="I32" s="134" t="n"/>
+      <c r="J32" s="134" t="n"/>
       <c r="K32" s="102" t="n"/>
       <c r="L32" s="102" t="n"/>
       <c r="M32" s="102" t="n"/>
@@ -2948,18 +2945,18 @@
       <c r="A33" s="81" t="n">
         <v>7</v>
       </c>
-      <c r="B33" s="142">
+      <c r="B33" s="141">
         <f>B32*1.05</f>
         <v/>
       </c>
       <c r="C33" s="102" t="n"/>
       <c r="D33" s="102" t="n"/>
       <c r="E33" s="102" t="n"/>
-      <c r="F33" s="135" t="n"/>
-      <c r="G33" s="140" t="n"/>
-      <c r="H33" s="140" t="n"/>
-      <c r="I33" s="135" t="n"/>
-      <c r="J33" s="135" t="n"/>
+      <c r="F33" s="134" t="n"/>
+      <c r="G33" s="139" t="n"/>
+      <c r="H33" s="139" t="n"/>
+      <c r="I33" s="134" t="n"/>
+      <c r="J33" s="134" t="n"/>
       <c r="K33" s="102" t="n"/>
       <c r="L33" s="102" t="n"/>
       <c r="M33" s="102" t="n"/>
@@ -2973,7 +2970,7 @@
       <c r="A34" s="75" t="n">
         <v>8</v>
       </c>
-      <c r="B34" s="143">
+      <c r="B34" s="142">
         <f>B33*1.05</f>
         <v/>
       </c>
@@ -2983,8 +2980,8 @@
       <c r="F34" s="102" t="n"/>
       <c r="G34" s="102" t="n"/>
       <c r="H34" s="102" t="n"/>
-      <c r="I34" s="135" t="n"/>
-      <c r="J34" s="135" t="n"/>
+      <c r="I34" s="134" t="n"/>
+      <c r="J34" s="134" t="n"/>
       <c r="K34" s="102" t="n"/>
       <c r="L34" s="102" t="n"/>
       <c r="M34" s="102" t="n"/>
@@ -2998,7 +2995,7 @@
       <c r="A35" s="81" t="n">
         <v>9</v>
       </c>
-      <c r="B35" s="142">
+      <c r="B35" s="141">
         <f>B34*1.05</f>
         <v/>
       </c>
@@ -3008,8 +3005,8 @@
       <c r="F35" s="102" t="n"/>
       <c r="G35" s="102" t="n"/>
       <c r="H35" s="102" t="n"/>
-      <c r="I35" s="135" t="n"/>
-      <c r="J35" s="135" t="n"/>
+      <c r="I35" s="134" t="n"/>
+      <c r="J35" s="134" t="n"/>
       <c r="K35" s="102" t="n"/>
       <c r="L35" s="102" t="n"/>
       <c r="M35" s="102" t="n"/>
@@ -3023,7 +3020,7 @@
       <c r="A36" s="75" t="n">
         <v>10</v>
       </c>
-      <c r="B36" s="143">
+      <c r="B36" s="142">
         <f>B35*1.05</f>
         <v/>
       </c>
@@ -3110,7 +3107,7 @@
           <t>제품 교체비용[매3년]</t>
         </is>
       </c>
-      <c r="B40" s="144">
+      <c r="B40" s="143">
         <f>ROUNDDOWN((8/3),0)</f>
         <v/>
       </c>
@@ -3137,7 +3134,7 @@
           <t>led평균단가(제품+시설)</t>
         </is>
       </c>
-      <c r="B41" s="143" t="n">
+      <c r="B41" s="142" t="n">
         <v>30000</v>
       </c>
       <c r="C41" s="102" t="n"/>
@@ -3159,7 +3156,7 @@
     </row>
     <row r="42" ht="21" customHeight="1" s="59" thickBot="1">
       <c r="A42" s="103" t="n"/>
-      <c r="B42" s="143">
+      <c r="B42" s="142">
         <f>B41*B40*B5</f>
         <v/>
       </c>
